--- a/data/trans_orig/P16A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7998</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>24591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5931</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39537</t>
+          <t>37690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448466</t>
+          <t>449185</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465778</t>
+          <t>465508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287418</t>
+          <t>287219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300749</t>
+          <t>300852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740920</t>
+          <t>742767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762529</t>
+          <t>763675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>24521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>31502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353825</t>
+          <t>353464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365030</t>
+          <t>365034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348010</t>
+          <t>347344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363050</t>
+          <t>363105</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708567</t>
+          <t>707297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725979</t>
+          <t>725882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22007</t>
+          <t>21672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14944</t>
+          <t>14703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31784</t>
+          <t>31739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520382</t>
+          <t>520717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534118</t>
+          <t>534253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152838</t>
+          <t>153079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163954</t>
+          <t>163962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678387</t>
+          <t>678432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>695782</t>
+          <t>695677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>43840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49517</t>
+          <t>51078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53715</t>
+          <t>54257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86021</t>
+          <t>87798</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1194667</t>
+          <t>1194494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1216381</t>
+          <t>1215924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>664768</t>
+          <t>663207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>688349</t>
+          <t>688377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1866599</t>
+          <t>1864822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898905</t>
+          <t>1898363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28157</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52106</t>
+          <t>52806</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39748</t>
+          <t>39510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68297</t>
+          <t>68221</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326844</t>
+          <t>325815</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341878</t>
+          <t>341811</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>516646</t>
+          <t>515946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540595</t>
+          <t>539760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>849992</t>
+          <t>850068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>878541</t>
+          <t>878779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>10770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55885</t>
+          <t>53629</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88254</t>
+          <t>85113</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58787</t>
+          <t>58593</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91478</t>
+          <t>91440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287223</t>
+          <t>287431</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297208</t>
+          <t>297222</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1160506</t>
+          <t>1163647</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1192875</t>
+          <t>1195131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1455482</t>
+          <t>1455520</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1488173</t>
+          <t>1488367</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67332</t>
+          <t>67282</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104432</t>
+          <t>103923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>152084</t>
+          <t>154794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205221</t>
+          <t>206173</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>230934</t>
+          <t>233067</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295516</t>
+          <t>296895</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3164740</t>
+          <t>3165249</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3201840</t>
+          <t>3201890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3172903</t>
+          <t>3171951</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3226040</t>
+          <t>3223330</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6351780</t>
+          <t>6350401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6416362</t>
+          <t>6414229</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26484</t>
+          <t>25110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>19559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15452</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39825</t>
+          <t>37530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410727</t>
+          <t>412101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>429949</t>
+          <t>430132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294938</t>
+          <t>294895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>308779</t>
+          <t>309063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>711840</t>
+          <t>714135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>736213</t>
+          <t>736058</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10697</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27277</t>
+          <t>27556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23289</t>
+          <t>23893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49552</t>
+          <t>47717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>389547</t>
+          <t>388571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408732</t>
+          <t>408307</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308038</t>
+          <t>307759</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324618</t>
+          <t>324955</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702781</t>
+          <t>704616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>729044</t>
+          <t>728440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35471</t>
+          <t>35847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40979</t>
+          <t>39643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73270</t>
+          <t>70421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>585701</t>
+          <t>583930</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>608956</t>
+          <t>609327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223617</t>
+          <t>223241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>243154</t>
+          <t>243730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>814147</t>
+          <t>816996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>846438</t>
+          <t>847774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24648</t>
+          <t>24830</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49574</t>
+          <t>49243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36994</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67158</t>
+          <t>68439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67581</t>
+          <t>68284</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109352</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1107741</t>
+          <t>1108072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1132667</t>
+          <t>1132485</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>698485</t>
+          <t>697204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>726750</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1813607</t>
+          <t>1815453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1855378</t>
+          <t>1854675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>49467</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80450</t>
+          <t>82267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61819</t>
+          <t>62140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95918</t>
+          <t>95539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488063</t>
+          <t>488325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502328</t>
+          <t>502705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>677918</t>
+          <t>676101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>707514</t>
+          <t>708901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1173046</t>
+          <t>1173425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1207145</t>
+          <t>1206824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64647</t>
+          <t>66267</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101710</t>
+          <t>102126</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68151</t>
+          <t>68746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106545</t>
+          <t>106192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253717</t>
+          <t>253752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264842</t>
+          <t>264905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1004530</t>
+          <t>1004114</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1041593</t>
+          <t>1039973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1265536</t>
+          <t>1265889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1303930</t>
+          <t>1303335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>90444</t>
+          <t>91400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137313</t>
+          <t>134513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224284</t>
+          <t>221060</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287681</t>
+          <t>283789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325041</t>
+          <t>325136</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>402682</t>
+          <t>406038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3278997</t>
+          <t>3281797</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3325866</t>
+          <t>3324910</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3251427</t>
+          <t>3255319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3314824</t>
+          <t>3318048</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6552736</t>
+          <t>6549380</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6630377</t>
+          <t>6630282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19873</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39520</t>
+          <t>40168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400487</t>
+          <t>402006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418287</t>
+          <t>418963</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>327695</t>
+          <t>327481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341743</t>
+          <t>341202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>736627</t>
+          <t>735979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756274</t>
+          <t>757477</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>19550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25020</t>
+          <t>25411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>17963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>39629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356364</t>
+          <t>357677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371361</t>
+          <t>371276</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>347253</t>
+          <t>346862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364298</t>
+          <t>363908</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709618</t>
+          <t>709871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732461</t>
+          <t>731537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24756</t>
+          <t>23433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23052</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42876</t>
+          <t>42549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>497158</t>
+          <t>498481</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513101</t>
+          <t>513782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143071</t>
+          <t>141907</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157789</t>
+          <t>157435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645160</t>
+          <t>645487</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>667015</t>
+          <t>668103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30798</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>57086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49485</t>
+          <t>48259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81283</t>
+          <t>80199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85764</t>
+          <t>86040</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127626</t>
+          <t>126446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1090608</t>
+          <t>1092552</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1118840</t>
+          <t>1119008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744593</t>
+          <t>745677</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>776391</t>
+          <t>777617</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1847888</t>
+          <t>1849068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1889750</t>
+          <t>1889474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18269</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37351</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68517</t>
+          <t>69024</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105035</t>
+          <t>102134</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92125</t>
+          <t>92678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133882</t>
+          <t>135308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>583355</t>
+          <t>582446</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>602437</t>
+          <t>602185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>633209</t>
+          <t>636110</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>669727</t>
+          <t>669220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1225068</t>
+          <t>1223642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1266825</t>
+          <t>1266272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>62095</t>
+          <t>63144</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99914</t>
+          <t>99403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67242</t>
+          <t>66372</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105765</t>
+          <t>104881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276093</t>
+          <t>276036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285194</t>
+          <t>285234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>982111</t>
+          <t>982622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1019930</t>
+          <t>1018881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1263405</t>
+          <t>1264289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1301928</t>
+          <t>1302798</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97995</t>
+          <t>97355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>143856</t>
+          <t>140152</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>237365</t>
+          <t>235648</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301554</t>
+          <t>302365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>347734</t>
+          <t>350038</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>428015</t>
+          <t>427679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3241866</t>
+          <t>3245570</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3287727</t>
+          <t>3288367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3230042</t>
+          <t>3229231</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3294231</t>
+          <t>3295948</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6489303</t>
+          <t>6489639</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6569584</t>
+          <t>6567280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44126</t>
+          <t>43300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477084</t>
+          <t>476910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493236</t>
+          <t>493347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>427243</t>
+          <t>426926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439624</t>
+          <t>438981</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>908553</t>
+          <t>909379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>929493</t>
+          <t>929480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8300</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>23457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16715</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31803</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49894</t>
+          <t>50891</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429547</t>
+          <t>428756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443913</t>
+          <t>443706</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>350777</t>
+          <t>351227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365865</t>
+          <t>366363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>784899</t>
+          <t>783902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>806679</t>
+          <t>806200</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48028</t>
+          <t>49034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24494</t>
+          <t>25753</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68447</t>
+          <t>66753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620236</t>
+          <t>619230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658929</t>
+          <t>659060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>140540</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153899</t>
+          <t>153682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>766109</t>
+          <t>767803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817549</t>
+          <t>817619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33917</t>
+          <t>33794</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59062</t>
+          <t>58036</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82129</t>
+          <t>82787</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73665</t>
+          <t>76542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128161</t>
+          <t>127321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>975757</t>
+          <t>976783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1000902</t>
+          <t>1001025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>895068</t>
+          <t>894410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946650</t>
+          <t>946712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1883855</t>
+          <t>1884695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1938351</t>
+          <t>1935474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42244</t>
+          <t>41789</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67056</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110298</t>
+          <t>113342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96506</t>
+          <t>97135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140068</t>
+          <t>143375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431315</t>
+          <t>431770</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>453077</t>
+          <t>453080</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>728698</t>
+          <t>725654</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>771940</t>
+          <t>772307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1172487</t>
+          <t>1169180</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1216049</t>
+          <t>1215420</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14997</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66574</t>
+          <t>66773</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>95403</t>
+          <t>94806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>72083</t>
+          <t>71626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101510</t>
+          <t>102783</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225510</t>
+          <t>225851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237865</t>
+          <t>237932</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>664749</t>
+          <t>665346</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>693578</t>
+          <t>693379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>899149</t>
+          <t>897876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>928576</t>
+          <t>929033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110886</t>
+          <t>110088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164561</t>
+          <t>166428</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>232594</t>
+          <t>230906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>318268</t>
+          <t>320275</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>357953</t>
+          <t>361996</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>473178</t>
+          <t>470530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3210013</t>
+          <t>3208146</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3263688</t>
+          <t>3264486</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3254417</t>
+          <t>3252410</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3340091</t>
+          <t>3341779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6474081</t>
+          <t>6476729</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6589306</t>
+          <t>6585263</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A05-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8268</t>
+          <t>8191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19461</t>
+          <t>20328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37690</t>
+          <t>37126</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449185</t>
+          <t>449201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465508</t>
+          <t>465585</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287219</t>
+          <t>286352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300852</t>
+          <t>300700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742767</t>
+          <t>743331</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>763675</t>
+          <t>763117</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>12539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12917</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31502</t>
+          <t>32193</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>353464</t>
+          <t>354395</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>365034</t>
+          <t>365106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>347344</t>
+          <t>348791</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363105</t>
+          <t>363072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>707297</t>
+          <t>706606</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725882</t>
+          <t>726008</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21672</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31739</t>
+          <t>33110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520717</t>
+          <t>520537</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534253</t>
+          <t>535082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153079</t>
+          <t>153679</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163962</t>
+          <t>164066</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678432</t>
+          <t>677061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>695677</t>
+          <t>695814</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51078</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54257</t>
+          <t>55233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87798</t>
+          <t>88057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1194494</t>
+          <t>1194274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1215924</t>
+          <t>1216187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>663207</t>
+          <t>661925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>688377</t>
+          <t>686828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1864822</t>
+          <t>1864563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898363</t>
+          <t>1897387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>22013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>28008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52806</t>
+          <t>52157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39510</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68221</t>
+          <t>70273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325815</t>
+          <t>327524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>341811</t>
+          <t>341354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>515946</t>
+          <t>516595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539760</t>
+          <t>540744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>850068</t>
+          <t>848016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>878779</t>
+          <t>877866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53629</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85113</t>
+          <t>86999</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58593</t>
+          <t>57347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91440</t>
+          <t>90616</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287431</t>
+          <t>286404</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>297222</t>
+          <t>296580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1163647</t>
+          <t>1161761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1195131</t>
+          <t>1195990</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1455520</t>
+          <t>1456344</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1488367</t>
+          <t>1489613</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67282</t>
+          <t>66243</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103923</t>
+          <t>102726</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154794</t>
+          <t>151239</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206173</t>
+          <t>205992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233067</t>
+          <t>234742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>296895</t>
+          <t>295749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3165249</t>
+          <t>3166446</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3201890</t>
+          <t>3202929</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3171951</t>
+          <t>3172132</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3223330</t>
+          <t>3226885</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6350401</t>
+          <t>6351547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6414229</t>
+          <t>6412554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>26233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>37332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412101</t>
+          <t>410978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430132</t>
+          <t>429593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294895</t>
+          <t>295477</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>309063</t>
+          <t>309183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>714135</t>
+          <t>714333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>736058</t>
+          <t>735674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>27871</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>23033</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47717</t>
+          <t>47853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388571</t>
+          <t>390038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>408307</t>
+          <t>408741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>307759</t>
+          <t>307444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324955</t>
+          <t>325171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704616</t>
+          <t>704480</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728440</t>
+          <t>729300</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19002</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>42941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35847</t>
+          <t>35785</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39643</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>583930</t>
+          <t>585388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>609327</t>
+          <t>610046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223241</t>
+          <t>223303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>243730</t>
+          <t>242805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>847774</t>
+          <t>846200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>25164</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49243</t>
+          <t>49363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68439</t>
+          <t>67524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68284</t>
+          <t>68955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107506</t>
+          <t>108879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1108072</t>
+          <t>1107952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1132485</t>
+          <t>1132151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>697204</t>
+          <t>698119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>726750</t>
+          <t>726687</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1815453</t>
+          <t>1814080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1854675</t>
+          <t>1854004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49467</t>
+          <t>50944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82267</t>
+          <t>83943</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62140</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95539</t>
+          <t>96730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>488325</t>
+          <t>488300</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502705</t>
+          <t>502593</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>676101</t>
+          <t>674425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>708901</t>
+          <t>707424</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1173425</t>
+          <t>1172234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1206824</t>
+          <t>1205826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66267</t>
+          <t>66529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102126</t>
+          <t>103105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68746</t>
+          <t>69170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106192</t>
+          <t>106559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253752</t>
+          <t>254704</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264905</t>
+          <t>264906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1004114</t>
+          <t>1003135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1039973</t>
+          <t>1039711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1265889</t>
+          <t>1265522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1303335</t>
+          <t>1302911</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91400</t>
+          <t>92506</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134513</t>
+          <t>136510</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>221060</t>
+          <t>224078</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283789</t>
+          <t>283076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325136</t>
+          <t>324671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>406038</t>
+          <t>403780</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3281797</t>
+          <t>3279800</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3324910</t>
+          <t>3323804</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3255319</t>
+          <t>3256032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3318048</t>
+          <t>3315030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6549380</t>
+          <t>6551638</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6630282</t>
+          <t>6630747</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,47 +6038,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>18962</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>28716</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>19574</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>28716</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>18670</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40168</t>
+          <t>40882</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402006</t>
+          <t>401557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418963</t>
+          <t>418432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>327481</t>
+          <t>328093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341202</t>
+          <t>341173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735979</t>
+          <t>735265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>757477</t>
+          <t>756573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,48%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19550</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25411</t>
+          <t>25018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>17291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39629</t>
+          <t>37798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357677</t>
+          <t>356969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371276</t>
+          <t>371618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346862</t>
+          <t>347255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363908</t>
+          <t>364223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709871</t>
+          <t>711702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731537</t>
+          <t>732209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>24558</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19933</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42549</t>
+          <t>42503</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>498481</t>
+          <t>497356</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513782</t>
+          <t>512816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141907</t>
+          <t>141731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157435</t>
+          <t>157628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645487</t>
+          <t>645533</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>668103</t>
+          <t>667768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57086</t>
+          <t>58912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48259</t>
+          <t>49455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80199</t>
+          <t>78137</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86040</t>
+          <t>87227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126446</t>
+          <t>128490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1092552</t>
+          <t>1090726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1119008</t>
+          <t>1118178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>745677</t>
+          <t>747739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>777617</t>
+          <t>776421</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1849068</t>
+          <t>1847024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1889474</t>
+          <t>1888287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18521</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37873</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69024</t>
+          <t>68077</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102134</t>
+          <t>104354</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92678</t>
+          <t>92944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135308</t>
+          <t>133266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>582446</t>
+          <t>582833</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>602185</t>
+          <t>602771</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>636110</t>
+          <t>633890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>669220</t>
+          <t>670167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1223642</t>
+          <t>1225684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1266272</t>
+          <t>1266006</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>63903</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99403</t>
+          <t>102684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66372</t>
+          <t>66903</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104881</t>
+          <t>104188</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276036</t>
+          <t>275722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285234</t>
+          <t>285194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>982622</t>
+          <t>979341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1018881</t>
+          <t>1018122</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1264289</t>
+          <t>1264982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1302798</t>
+          <t>1302267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>97355</t>
+          <t>96399</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140152</t>
+          <t>142797</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235648</t>
+          <t>237424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>302365</t>
+          <t>303025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>350038</t>
+          <t>350646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>427679</t>
+          <t>429680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3245570</t>
+          <t>3242925</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3288367</t>
+          <t>3289323</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3229231</t>
+          <t>3228571</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3295948</t>
+          <t>3294172</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6489639</t>
+          <t>6487638</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6567280</t>
+          <t>6566672</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>27811</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20541</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31759</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43300</t>
+          <t>47038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>486829</t>
+          <t>531460</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476910</t>
+          <t>522807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493347</t>
+          <t>539405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>434092</t>
+          <t>473249</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>426926</t>
+          <t>465922</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438981</t>
+          <t>478888</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>920920</t>
+          <t>1004709</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>909379</t>
+          <t>991991</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>929480</t>
+          <t>1014451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>14748</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8507</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23457</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23572</t>
+          <t>26253</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>18680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31353</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>37929</t>
+          <t>41001</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50891</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>437855</t>
+          <t>468464</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428756</t>
+          <t>459497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>443706</t>
+          <t>474864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>359008</t>
+          <t>396890</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351227</t>
+          <t>387562</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366363</t>
+          <t>404463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>796864</t>
+          <t>865354</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783902</t>
+          <t>851974</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>806200</t>
+          <t>874596</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>26968</t>
+          <t>27845</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>19021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49034</t>
+          <t>40321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>19636</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44505</t>
+          <t>47482</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>36205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66753</t>
+          <t>61521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>641296</t>
+          <t>443767</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619230</t>
+          <t>431291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659060</t>
+          <t>452591</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148756</t>
+          <t>167183</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140540</t>
+          <t>159657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153682</t>
+          <t>173300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>790051</t>
+          <t>610949</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>767803</t>
+          <t>596910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>817619</t>
+          <t>622226</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166293</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166293</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166293</t>
+          <t>186819</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834556</t>
+          <t>658431</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834556</t>
+          <t>658431</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834556</t>
+          <t>658431</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45009</t>
+          <t>49314</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33794</t>
+          <t>37887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58036</t>
+          <t>63796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>61449</t>
+          <t>67234</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30485</t>
+          <t>55878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82787</t>
+          <t>80933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>106458</t>
+          <t>116549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76542</t>
+          <t>97018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127321</t>
+          <t>133958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>989810</t>
+          <t>1082529</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>976783</t>
+          <t>1068047</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1001025</t>
+          <t>1093956</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>915748</t>
+          <t>793050</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>894410</t>
+          <t>779351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946712</t>
+          <t>804406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1905558</t>
+          <t>1875578</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1884695</t>
+          <t>1858169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1935474</t>
+          <t>1895109</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>22627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41789</t>
+          <t>43826</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>89876</t>
+          <t>91563</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66689</t>
+          <t>78654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113342</t>
+          <t>105478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>119714</t>
+          <t>123547</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97135</t>
+          <t>106794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143375</t>
+          <t>141197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>443721</t>
+          <t>534497</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>431770</t>
+          <t>522655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>453080</t>
+          <t>543854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>749120</t>
+          <t>738564</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725654</t>
+          <t>724649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>772307</t>
+          <t>751473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1192841</t>
+          <t>1273061</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1169180</t>
+          <t>1255411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1215420</t>
+          <t>1289814</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6475</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>78741</t>
+          <t>86652</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66773</t>
+          <t>72254</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94806</t>
+          <t>102688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>85216</t>
+          <t>93261</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71626</t>
+          <t>77040</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102783</t>
+          <t>110248</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>234032</t>
+          <t>230619</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225851</t>
+          <t>221587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237932</t>
+          <t>234469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>681411</t>
+          <t>756341</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>665346</t>
+          <t>740305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>693379</t>
+          <t>770739</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>915443</t>
+          <t>986960</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>897876</t>
+          <t>969973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>929033</t>
+          <t>1003181</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>141030</t>
+          <t>149658</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110088</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166428</t>
+          <t>174459</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>284551</t>
+          <t>306500</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230906</t>
+          <t>281501</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>320275</t>
+          <t>334017</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>425581</t>
+          <t>456159</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>361996</t>
+          <t>417275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470530</t>
+          <t>493846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3233544</t>
+          <t>3291335</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3208146</t>
+          <t>3266534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3264486</t>
+          <t>3315725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3288134</t>
+          <t>3325277</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3252410</t>
+          <t>3297760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3341779</t>
+          <t>3350276</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6521678</t>
+          <t>6616612</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6476729</t>
+          <t>6578925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6585263</t>
+          <t>6655496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572685</t>
+          <t>3631777</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572685</t>
+          <t>3631777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572685</t>
+          <t>3631777</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947259</t>
+          <t>7072771</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947259</t>
+          <t>7072771</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947259</t>
+          <t>7072771</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
